--- a/diseases/d149/2015-2019.xlsx
+++ b/diseases/d149/2015-2019.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1066,6 +1076,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1211,6 +1226,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1356,6 +1376,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1501,6 +1526,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1646,6 +1676,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1791,6 +1826,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1927,6 +1967,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2075,6 +2120,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2220,6 +2270,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2365,6 +2420,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2510,6 +2570,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2655,6 +2720,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2800,6 +2870,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2945,6 +3020,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3090,6 +3170,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3235,6 +3320,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3383,6 +3473,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3528,6 +3623,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3664,6 +3764,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3809,6 +3914,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3945,6 +4055,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4090,6 +4205,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4235,6 +4355,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4380,6 +4505,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4525,6 +4655,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4673,6 +4808,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4818,6 +4958,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4963,6 +5108,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5108,6 +5258,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5253,6 +5408,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5398,6 +5558,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5543,6 +5708,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5688,6 +5858,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5833,6 +6008,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5981,6 +6161,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6126,6 +6311,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6271,6 +6461,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6416,6 +6611,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6552,6 +6752,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6688,6 +6893,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6833,6 +7043,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6978,6 +7193,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7123,6 +7343,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7271,6 +7496,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7416,6 +7646,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7561,6 +7796,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7706,6 +7946,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7851,6 +8096,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7996,6 +8246,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8141,6 +8396,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8286,6 +8546,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8431,6 +8696,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8579,6 +8849,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8724,6 +8999,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8869,6 +9149,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9014,6 +9299,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9159,6 +9449,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9304,6 +9599,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9449,6 +9749,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9594,6 +9899,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9730,6 +10040,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9878,6 +10193,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10023,6 +10343,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10168,6 +10493,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10313,6 +10643,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10458,6 +10793,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10603,6 +10943,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10748,6 +11093,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10893,6 +11243,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11038,6 +11393,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11186,6 +11546,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11331,6 +11696,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11476,6 +11846,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11621,6 +11996,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11766,6 +12146,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11911,6 +12296,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12056,6 +12446,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12201,6 +12596,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12346,6 +12746,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12494,6 +12899,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12639,6 +13049,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12784,6 +13199,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12929,6 +13349,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13074,6 +13499,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13219,6 +13649,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13364,6 +13799,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13509,6 +13949,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13654,6 +14099,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13802,6 +14252,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13947,6 +14402,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14092,6 +14552,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14237,6 +14702,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14382,6 +14852,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14527,6 +15002,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14672,6 +15152,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14808,6 +15293,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14953,6 +15443,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15101,6 +15596,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15246,6 +15746,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15391,6 +15896,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15536,6 +16046,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15672,6 +16187,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15817,6 +16337,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15962,6 +16487,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16098,6 +16628,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16243,6 +16778,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16391,6 +16931,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16536,6 +17081,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16681,6 +17231,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16826,6 +17381,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16971,6 +17531,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17107,6 +17672,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17252,6 +17822,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17388,6 +17963,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17533,6 +18113,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17681,6 +18266,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17826,6 +18416,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17971,6 +18566,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18116,6 +18716,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18261,6 +18866,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18397,6 +19007,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18542,6 +19157,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18678,6 +19298,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18823,6 +19448,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18971,6 +19601,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19116,6 +19751,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19252,6 +19892,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19397,6 +20042,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19542,6 +20192,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19687,6 +20342,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19832,6 +20492,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19968,6 +20633,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20104,6 +20774,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20252,6 +20927,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20397,6 +21077,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20542,6 +21227,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20678,6 +21368,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20823,6 +21518,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20968,6 +21668,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21104,6 +21809,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21240,6 +21950,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21376,6 +22091,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21524,6 +22244,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21669,6 +22394,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21805,6 +22535,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21950,6 +22685,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22095,6 +22835,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22240,6 +22985,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22385,6 +23135,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22530,6 +23285,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22675,6 +23435,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22823,6 +23588,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22968,6 +23738,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23104,6 +23879,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23249,6 +24029,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23385,6 +24170,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23530,6 +24320,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23675,6 +24470,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23811,6 +24611,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23956,6 +24761,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24104,6 +24914,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24249,6 +25064,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24385,6 +25205,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24530,6 +25355,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24675,6 +25505,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24820,6 +25655,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24965,6 +25805,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25110,6 +25955,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25246,6 +26096,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25394,6 +26249,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25539,6 +26399,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25675,6 +26540,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25820,6 +26690,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25956,6 +26831,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26101,6 +26981,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26246,6 +27131,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26382,6 +27272,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26518,6 +27413,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26666,6 +27566,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26811,6 +27716,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26956,6 +27866,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27101,6 +28016,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27237,6 +28157,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27382,6 +28307,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27527,6 +28457,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27663,6 +28598,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27799,6 +28739,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27947,6 +28892,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28083,6 +29033,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28228,6 +29183,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28373,6 +29333,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28509,6 +29474,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28654,6 +29624,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28799,6 +29774,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28944,6 +29924,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29080,6 +30065,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29228,6 +30218,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29373,6 +30368,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29509,6 +30509,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29654,6 +30659,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29790,6 +30800,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29935,6 +30950,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30080,6 +31100,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30225,6 +31250,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30370,6 +31400,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30518,6 +31553,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30663,6 +31703,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30808,6 +31853,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30953,6 +32003,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31089,6 +32144,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31234,6 +32294,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO214" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31379,6 +32444,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31524,6 +32594,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31669,6 +32744,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31817,6 +32897,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31962,6 +33047,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32098,6 +33188,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32243,6 +33338,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32379,6 +33479,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32524,6 +33629,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32669,6 +33779,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32805,6 +33920,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32950,6 +34070,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO226" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33098,6 +34223,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO227" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33243,6 +34373,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33388,6 +34523,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO229" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33533,6 +34673,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33678,6 +34823,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO231" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33823,6 +34973,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33968,6 +35123,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34113,6 +35273,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO234" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34258,6 +35423,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO235" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34406,6 +35576,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34551,6 +35726,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34687,6 +35867,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34832,6 +36017,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO239" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34977,6 +36167,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35122,6 +36317,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO241" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35267,6 +36467,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35412,6 +36617,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35548,6 +36758,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35696,6 +36911,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35841,6 +37061,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO246" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35977,6 +37202,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO247" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36122,6 +37352,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36258,6 +37493,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO249" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36403,6 +37643,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36548,6 +37793,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO251" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36693,6 +37943,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36838,6 +38093,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO253" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36986,6 +38246,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO254" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37131,6 +38396,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO255" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37276,6 +38546,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37421,6 +38696,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO257" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37557,6 +38837,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO258" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37702,6 +38987,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO259" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37847,6 +39137,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO260" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37992,6 +39287,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38137,6 +39437,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO262" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38285,6 +39590,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38430,6 +39740,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO264" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38566,6 +39881,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO265" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38711,6 +40031,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO266" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38847,6 +40172,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO267" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38992,6 +40322,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39137,6 +40472,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39282,6 +40622,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO270" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39427,6 +40772,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO271" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39575,6 +40925,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO272" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39720,6 +41075,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO273" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39865,6 +41225,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO274" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40010,6 +41375,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO275" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40155,6 +41525,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO276" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40300,6 +41675,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO277" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40445,6 +41825,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO278" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40590,6 +41975,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO279" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40735,6 +42125,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO280" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40883,6 +42278,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO281" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41028,6 +42428,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO282" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41164,6 +42569,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO283" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41309,6 +42719,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO284" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41454,6 +42869,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO285" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41599,6 +43019,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO286" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41744,6 +43169,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO287" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41889,6 +43319,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO288" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42034,6 +43469,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO289" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42182,6 +43622,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO290" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42327,6 +43772,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO291" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42472,6 +43922,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO292" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42617,6 +44072,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO293" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42762,6 +44222,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO294" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42907,6 +44372,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO295" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43052,6 +44522,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO296" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43197,6 +44672,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO297" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43342,6 +44822,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO298" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43490,6 +44975,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA299" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO299" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43626,6 +45116,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA300" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO300" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43771,6 +45266,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA301" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO301" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43916,6 +45416,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO302" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44052,6 +45557,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA303" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO303" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44197,6 +45707,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA304" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO304" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44342,6 +45857,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA305" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO305" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44487,6 +46007,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO306" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44632,6 +46157,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO307" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44780,6 +46310,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA308" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO308" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44925,6 +46460,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA309" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO309" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45070,6 +46610,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA310" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO310" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45215,6 +46760,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA311" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO311" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45360,6 +46910,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO312" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45505,6 +47060,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA313" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO313" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45650,6 +47210,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO314" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45795,6 +47360,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA315" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO315" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45940,6 +47510,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO316" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46088,6 +47663,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO317" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46233,6 +47813,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO318" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46378,6 +47963,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO319" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46523,6 +48113,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO320" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46668,6 +48263,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO321" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46813,6 +48413,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO322" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46958,6 +48563,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO323" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47103,6 +48713,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA324" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO324" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47248,6 +48863,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA325" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO325" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47396,6 +49016,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA326" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO326" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47541,6 +49166,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA327" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO327" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47686,6 +49316,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA328" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO328" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47831,6 +49466,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA329" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO329" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47976,6 +49616,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA330" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO330" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48121,6 +49766,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA331" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO331" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48266,6 +49916,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA332" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO332" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48411,6 +50066,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA333" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO333" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48556,6 +50216,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA334" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO334" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48704,6 +50369,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA335" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO335" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48849,6 +50519,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA336" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO336" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48994,6 +50669,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA337" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO337" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49139,6 +50819,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA338" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO338" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49275,6 +50960,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA339" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO339" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49420,6 +51110,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA340" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO340" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49565,6 +51260,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA341" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO341" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49710,6 +51410,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA342" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO342" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49855,6 +51560,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA343" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO343" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50003,6 +51713,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA344" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO344" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50148,6 +51863,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA345" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO345" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50293,6 +52013,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA346" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO346" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50438,6 +52163,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA347" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO347" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50583,6 +52313,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA348" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO348" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50728,6 +52463,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA349" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO349" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50873,6 +52613,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA350" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO350" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51018,6 +52763,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA351" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO351" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51163,6 +52913,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA352" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO352" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51311,6 +53066,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA353" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO353" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51456,6 +53216,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA354" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO354" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51601,6 +53366,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA355" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO355" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51746,6 +53516,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA356" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO356" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51891,6 +53666,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA357" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO357" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52036,6 +53816,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA358" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO358" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52181,6 +53966,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA359" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO359" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52326,6 +54116,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA360" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO360" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52471,6 +54266,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA361" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO361" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52619,6 +54419,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA362" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO362" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52764,6 +54569,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA363" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO363" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52909,6 +54719,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO364" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53054,6 +54869,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA365" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO365" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53199,6 +55019,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA366" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO366" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53344,6 +55169,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA367" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO367" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53489,6 +55319,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA368" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO368" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53625,6 +55460,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA369" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO369" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53770,6 +55610,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA370" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO370" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53918,6 +55763,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA371" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO371" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54063,6 +55913,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA372" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO372" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54208,6 +56063,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA373" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO373" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54353,6 +56213,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA374" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO374" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54498,6 +56363,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA375" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO375" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54643,6 +56513,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA376" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO376" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54788,6 +56663,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA377" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO377" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54933,6 +56813,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA378" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO378" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55078,6 +56963,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA379" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO379" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55226,6 +57116,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA380" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO380" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55371,6 +57266,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA381" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO381" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55516,6 +57416,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA382" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO382" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55661,6 +57566,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA383" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO383" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55797,6 +57707,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA384" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO384" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55942,6 +57857,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA385" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO385" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56087,6 +58007,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA386" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO386" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56232,6 +58157,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA387" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO387" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56377,6 +58307,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA388" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO388" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56525,6 +58460,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA389" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO389" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56670,6 +58610,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA390" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO390" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56815,6 +58760,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA391" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO391" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56960,6 +58910,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA392" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO392" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57105,6 +59060,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA393" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO393" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57250,6 +59210,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA394" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO394" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57395,6 +59360,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA395" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO395" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57540,6 +59510,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA396" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO396" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57685,6 +59660,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA397" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO397" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57833,6 +59813,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA398" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO398" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57978,6 +59963,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA399" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO399" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58123,6 +60113,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA400" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO400" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58268,6 +60263,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA401" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO401" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58413,6 +60413,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA402" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO402" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58558,6 +60563,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA403" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO403" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58703,6 +60713,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA404" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO404" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58839,6 +60854,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA405" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO405" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58984,6 +61004,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA406" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO406" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59132,6 +61157,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA407" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO407" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59277,6 +61307,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA408" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO408" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59413,6 +61448,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA409" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO409" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59558,6 +61598,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA410" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO410" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59703,6 +61748,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA411" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO411" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59848,6 +61898,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA412" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO412" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59993,6 +62048,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA413" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO413" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60138,6 +62198,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA414" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO414" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60283,6 +62348,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA415" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO415" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60431,6 +62501,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA416" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO416" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60576,6 +62651,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA417" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO417" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60712,6 +62792,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA418" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO418" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60857,6 +62942,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA419" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO419" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61002,6 +63092,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA420" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO420" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61147,6 +63242,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA421" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO421" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61292,6 +63392,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA422" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO422" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61437,6 +63542,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA423" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO423" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61582,6 +63692,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA424" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO424" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61730,6 +63845,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA425" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO425" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61875,6 +63995,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA426" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO426" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62020,6 +64145,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA427" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO427" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62165,6 +64295,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA428" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO428" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62301,6 +64436,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA429" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO429" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62446,6 +64586,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA430" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO430" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62591,6 +64736,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA431" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO431" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62727,6 +64877,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA432" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO432" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62872,6 +65027,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA433" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO433" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63020,6 +65180,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA434" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO434" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63165,6 +65330,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA435" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO435" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63310,6 +65480,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA436" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO436" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63455,6 +65630,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA437" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO437" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63600,6 +65780,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA438" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO438" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63745,6 +65930,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA439" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO439" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63890,6 +66080,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA440" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO440" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64035,6 +66230,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA441" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO441" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64180,6 +66380,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA442" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO442" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64328,6 +66533,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA443" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO443" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64473,6 +66683,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA444" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO444" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64618,6 +66833,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA445" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO445" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64763,6 +66983,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA446" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO446" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64908,6 +67133,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA447" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO447" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65053,6 +67283,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA448" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO448" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65198,6 +67433,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA449" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO449" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65343,6 +67583,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA450" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO450" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65488,6 +67733,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA451" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO451" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65636,6 +67886,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA452" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO452" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65781,6 +68036,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA453" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO453" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65926,6 +68186,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA454" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO454" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66071,6 +68336,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA455" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO455" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66216,6 +68486,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA456" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO456" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66361,6 +68636,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA457" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO457" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66506,6 +68786,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA458" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO458" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66651,6 +68936,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA459" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO459" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66796,6 +69086,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA460" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO460" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66944,6 +69239,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA461" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO461" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67089,6 +69389,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA462" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO462" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67234,6 +69539,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA463" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO463" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67379,6 +69689,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA464" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO464" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67524,6 +69839,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA465" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO465" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67669,6 +69989,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA466" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO466" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67814,6 +70139,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA467" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO467" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67959,6 +70289,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA468" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO468" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68104,6 +70439,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA469" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO469" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68252,6 +70592,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA470" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO470" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68397,6 +70742,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA471" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO471" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68533,6 +70883,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA472" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO472" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68678,6 +71033,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA473" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO473" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68823,6 +71183,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA474" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO474" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68968,6 +71333,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA475" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO475" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69113,6 +71483,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA476" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO476" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69249,6 +71624,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA477" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO477" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69394,6 +71774,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA478" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO478" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69542,6 +71927,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA479" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO479" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69687,6 +72077,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA480" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO480" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69832,6 +72227,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA481" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO481" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69977,6 +72377,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA482" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO482" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70113,6 +72518,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA483" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO483" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70258,6 +72668,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA484" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO484" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70403,6 +72818,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA485" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO485" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70548,6 +72968,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA486" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO486" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70693,6 +73118,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA487" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO487" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70841,6 +73271,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA488" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO488" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70986,6 +73421,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA489" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO489" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71122,6 +73562,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA490" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO490" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71267,6 +73712,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA491" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO491" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71403,6 +73853,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA492" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO492" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71548,6 +74003,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA493" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO493" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71693,6 +74153,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA494" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO494" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71829,6 +74294,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA495" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO495" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71974,6 +74444,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA496" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO496" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72122,6 +74597,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA497" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO497" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72267,6 +74747,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA498" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO498" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72412,6 +74897,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA499" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO499" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72557,6 +75047,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA500" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO500" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72702,6 +75197,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA501" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO501" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72847,6 +75347,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA502" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO502" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72992,6 +75497,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA503" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO503" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73128,6 +75638,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA504" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO504" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73273,6 +75788,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA505" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO505" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73421,6 +75941,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA506" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO506" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73566,6 +76091,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA507" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO507" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73711,6 +76241,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA508" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO508" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73856,6 +76391,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA509" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO509" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73992,6 +76532,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA510" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO510" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -74137,6 +76682,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA511" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO511" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -74282,6 +76832,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA512" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO512" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -74427,6 +76982,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA513" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO513" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -74572,6 +77132,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA514" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO514" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -74720,6 +77285,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA515" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO515" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -74865,6 +77435,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA516" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO516" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -75010,6 +77585,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA517" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO517" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -75155,6 +77735,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA518" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO518" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -75300,6 +77885,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA519" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO519" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -75445,6 +78035,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA520" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO520" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -75590,6 +78185,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA521" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO521" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -75735,6 +78335,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA522" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO522" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -75880,6 +78485,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA523" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO523" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -76028,6 +78638,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA524" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO524" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -76173,6 +78788,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA525" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO525" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -76318,6 +78938,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA526" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO526" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -76463,6 +79088,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA527" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO527" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -76599,6 +79229,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA528" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO528" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -76744,6 +79379,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA529" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO529" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -76889,6 +79529,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA530" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO530" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -77034,6 +79679,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA531" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO531" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -77179,6 +79829,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA532" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO532" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -77327,6 +79982,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA533" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO533" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -77472,6 +80132,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA534" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO534" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -77617,6 +80282,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA535" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO535" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -77762,6 +80432,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA536" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO536" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -77907,6 +80582,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA537" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO537" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -78052,6 +80732,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA538" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO538" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -78197,6 +80882,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA539" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO539" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -78342,6 +81032,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA540" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO540" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -78485,6 +81180,11 @@
       <c r="S541" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA541" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO541" t="inlineStr">
